--- a/output/mariners_report_20260825.xlsx
+++ b/output/mariners_report_20260825.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roster Moves" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Targets" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deadline Simulation" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -149,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -334,6 +335,7 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7016,7 +7018,9 @@
           <t>PHI</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n"/>
+      <c r="E4" s="8" t="n">
+        <v/>
+      </c>
       <c r="F4" s="8" t="inlineStr"/>
       <c r="G4" s="8" t="inlineStr"/>
       <c r="H4" s="22" t="inlineStr"/>
@@ -7042,7 +7046,9 @@
           <t>PHI</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n"/>
+      <c r="E5" s="8" t="n">
+        <v/>
+      </c>
       <c r="F5" s="8" t="inlineStr"/>
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="22" t="inlineStr"/>
@@ -7068,7 +7074,9 @@
           <t>TOR</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n"/>
+      <c r="E6" s="8" t="n">
+        <v/>
+      </c>
       <c r="F6" s="8" t="inlineStr"/>
       <c r="G6" s="8" t="inlineStr"/>
       <c r="H6" s="22" t="inlineStr"/>
@@ -7094,7 +7102,9 @@
           <t>TOR</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n"/>
+      <c r="E7" s="8" t="n">
+        <v/>
+      </c>
       <c r="F7" s="8" t="inlineStr"/>
       <c r="G7" s="8" t="inlineStr"/>
       <c r="H7" s="22" t="inlineStr"/>
@@ -7120,7 +7130,9 @@
           <t>TOR</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n"/>
+      <c r="E8" s="8" t="n">
+        <v/>
+      </c>
       <c r="F8" s="8" t="inlineStr"/>
       <c r="G8" s="8" t="inlineStr"/>
       <c r="H8" s="22" t="inlineStr"/>
@@ -7146,7 +7158,9 @@
           <t>BOS</t>
         </is>
       </c>
-      <c r="E9" s="8" t="n"/>
+      <c r="E9" s="8" t="n">
+        <v/>
+      </c>
       <c r="F9" s="8" t="inlineStr"/>
       <c r="G9" s="8" t="inlineStr"/>
       <c r="H9" s="22" t="inlineStr"/>
@@ -7172,7 +7186,9 @@
           <t>BOS</t>
         </is>
       </c>
-      <c r="E10" s="8" t="n"/>
+      <c r="E10" s="8" t="n">
+        <v/>
+      </c>
       <c r="F10" s="8" t="inlineStr"/>
       <c r="G10" s="8" t="inlineStr"/>
       <c r="H10" s="22" t="inlineStr"/>
@@ -7245,7 +7261,9 @@
           <t>BOS</t>
         </is>
       </c>
-      <c r="E14" s="40" t="n"/>
+      <c r="E14" s="40" t="n">
+        <v/>
+      </c>
       <c r="F14" s="40" t="inlineStr"/>
       <c r="G14" s="40" t="inlineStr"/>
       <c r="H14" s="39" t="inlineStr"/>
@@ -7269,7 +7287,9 @@
           <t>ATH</t>
         </is>
       </c>
-      <c r="E15" s="8" t="n"/>
+      <c r="E15" s="8" t="n">
+        <v/>
+      </c>
       <c r="F15" s="8" t="inlineStr"/>
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="22" t="inlineStr"/>
@@ -7293,7 +7313,9 @@
           <t>ATH</t>
         </is>
       </c>
-      <c r="E16" s="8" t="n"/>
+      <c r="E16" s="8" t="n">
+        <v/>
+      </c>
       <c r="F16" s="8" t="inlineStr"/>
       <c r="G16" s="8" t="inlineStr"/>
       <c r="H16" s="22" t="inlineStr"/>
@@ -7317,7 +7339,9 @@
           <t>ATH</t>
         </is>
       </c>
-      <c r="E17" s="8" t="n"/>
+      <c r="E17" s="8" t="n">
+        <v/>
+      </c>
       <c r="F17" s="8" t="inlineStr"/>
       <c r="G17" s="8" t="inlineStr"/>
       <c r="H17" s="22" t="inlineStr"/>
@@ -7341,7 +7365,9 @@
           <t>ATH</t>
         </is>
       </c>
-      <c r="E18" s="8" t="n"/>
+      <c r="E18" s="8" t="n">
+        <v/>
+      </c>
       <c r="F18" s="8" t="inlineStr"/>
       <c r="G18" s="8" t="inlineStr"/>
       <c r="H18" s="22" t="inlineStr"/>
@@ -7365,7 +7391,9 @@
           <t>TEX</t>
         </is>
       </c>
-      <c r="E19" s="8" t="n"/>
+      <c r="E19" s="8" t="n">
+        <v/>
+      </c>
       <c r="F19" s="8" t="inlineStr"/>
       <c r="G19" s="8" t="inlineStr"/>
       <c r="H19" s="22" t="inlineStr"/>
@@ -7389,7 +7417,9 @@
           <t>TEX</t>
         </is>
       </c>
-      <c r="E20" s="8" t="n"/>
+      <c r="E20" s="8" t="n">
+        <v/>
+      </c>
       <c r="F20" s="8" t="inlineStr"/>
       <c r="G20" s="8" t="inlineStr"/>
       <c r="H20" s="22" t="inlineStr"/>
@@ -7413,7 +7443,9 @@
           <t>TEX</t>
         </is>
       </c>
-      <c r="E21" s="8" t="n"/>
+      <c r="E21" s="8" t="n">
+        <v/>
+      </c>
       <c r="F21" s="8" t="inlineStr"/>
       <c r="G21" s="8" t="inlineStr"/>
       <c r="H21" s="22" t="inlineStr"/>
@@ -7437,7 +7469,9 @@
           <t>ATH</t>
         </is>
       </c>
-      <c r="E22" s="8" t="n"/>
+      <c r="E22" s="8" t="n">
+        <v/>
+      </c>
       <c r="F22" s="8" t="inlineStr"/>
       <c r="G22" s="8" t="inlineStr"/>
       <c r="H22" s="22" t="inlineStr"/>
@@ -7461,7 +7495,9 @@
           <t>ATH</t>
         </is>
       </c>
-      <c r="E23" s="8" t="n"/>
+      <c r="E23" s="8" t="n">
+        <v/>
+      </c>
       <c r="F23" s="8" t="inlineStr"/>
       <c r="G23" s="8" t="inlineStr"/>
       <c r="H23" s="22" t="inlineStr"/>
@@ -7485,7 +7521,9 @@
           <t>ATH</t>
         </is>
       </c>
-      <c r="E24" s="8" t="n"/>
+      <c r="E24" s="8" t="n">
+        <v/>
+      </c>
       <c r="F24" s="8" t="inlineStr"/>
       <c r="G24" s="8" t="inlineStr"/>
       <c r="H24" s="22" t="inlineStr"/>
@@ -7509,7 +7547,9 @@
           <t>LAA</t>
         </is>
       </c>
-      <c r="E25" s="40" t="n"/>
+      <c r="E25" s="40" t="n">
+        <v/>
+      </c>
       <c r="F25" s="40" t="inlineStr"/>
       <c r="G25" s="40" t="inlineStr"/>
       <c r="H25" s="39" t="inlineStr"/>
@@ -7533,7 +7573,9 @@
           <t>LAA</t>
         </is>
       </c>
-      <c r="E26" s="40" t="n"/>
+      <c r="E26" s="40" t="n">
+        <v/>
+      </c>
       <c r="F26" s="40" t="inlineStr"/>
       <c r="G26" s="40" t="inlineStr"/>
       <c r="H26" s="39" t="inlineStr"/>
@@ -7557,7 +7599,9 @@
           <t>LAA</t>
         </is>
       </c>
-      <c r="E27" s="40" t="n"/>
+      <c r="E27" s="40" t="n">
+        <v/>
+      </c>
       <c r="F27" s="40" t="inlineStr"/>
       <c r="G27" s="40" t="inlineStr"/>
       <c r="H27" s="39" t="inlineStr"/>
@@ -7581,7 +7625,9 @@
           <t>COL</t>
         </is>
       </c>
-      <c r="E28" s="40" t="n"/>
+      <c r="E28" s="40" t="n">
+        <v/>
+      </c>
       <c r="F28" s="40" t="inlineStr"/>
       <c r="G28" s="40" t="inlineStr"/>
       <c r="H28" s="39" t="inlineStr"/>
@@ -7605,7 +7651,9 @@
           <t>COL</t>
         </is>
       </c>
-      <c r="E29" s="40" t="n"/>
+      <c r="E29" s="40" t="n">
+        <v/>
+      </c>
       <c r="F29" s="40" t="inlineStr"/>
       <c r="G29" s="40" t="inlineStr"/>
       <c r="H29" s="39" t="inlineStr"/>
@@ -7629,7 +7677,9 @@
           <t>COL</t>
         </is>
       </c>
-      <c r="E30" s="40" t="n"/>
+      <c r="E30" s="40" t="n">
+        <v/>
+      </c>
       <c r="F30" s="40" t="inlineStr"/>
       <c r="G30" s="40" t="inlineStr"/>
       <c r="H30" s="39" t="inlineStr"/>
@@ -7653,7 +7703,9 @@
           <t>HOU</t>
         </is>
       </c>
-      <c r="E31" s="40" t="n"/>
+      <c r="E31" s="40" t="n">
+        <v/>
+      </c>
       <c r="F31" s="40" t="inlineStr"/>
       <c r="G31" s="40" t="inlineStr"/>
       <c r="H31" s="39" t="inlineStr"/>
@@ -7677,7 +7729,9 @@
           <t>HOU</t>
         </is>
       </c>
-      <c r="E32" s="40" t="n"/>
+      <c r="E32" s="40" t="n">
+        <v/>
+      </c>
       <c r="F32" s="40" t="inlineStr"/>
       <c r="G32" s="40" t="inlineStr"/>
       <c r="H32" s="39" t="inlineStr"/>
@@ -7701,7 +7755,9 @@
           <t>LAA</t>
         </is>
       </c>
-      <c r="E33" s="40" t="n"/>
+      <c r="E33" s="40" t="n">
+        <v/>
+      </c>
       <c r="F33" s="40" t="inlineStr"/>
       <c r="G33" s="40" t="inlineStr"/>
       <c r="H33" s="39" t="inlineStr"/>
@@ -7725,7 +7781,9 @@
           <t>LAA</t>
         </is>
       </c>
-      <c r="E34" s="40" t="n"/>
+      <c r="E34" s="40" t="n">
+        <v/>
+      </c>
       <c r="F34" s="40" t="inlineStr"/>
       <c r="G34" s="40" t="inlineStr"/>
       <c r="H34" s="39" t="inlineStr"/>
@@ -7749,7 +7807,9 @@
           <t>LAA</t>
         </is>
       </c>
-      <c r="E35" s="40" t="n"/>
+      <c r="E35" s="40" t="n">
+        <v/>
+      </c>
       <c r="F35" s="40" t="inlineStr"/>
       <c r="G35" s="40" t="inlineStr"/>
       <c r="H35" s="39" t="inlineStr"/>
@@ -7773,7 +7833,9 @@
           <t>LAA</t>
         </is>
       </c>
-      <c r="E36" s="40" t="n"/>
+      <c r="E36" s="40" t="n">
+        <v/>
+      </c>
       <c r="F36" s="40" t="inlineStr"/>
       <c r="G36" s="40" t="inlineStr"/>
       <c r="H36" s="39" t="inlineStr"/>
@@ -7786,4 +7848,1738 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G108"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DEADLINE ACQUISITION SIMULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIO SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>RS/G</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>RA/G</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Win%</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Proj W</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Playoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>Baseline - no IL returns</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="C4" s="46" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="D4" s="41" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E4" s="40" t="n">
+        <v>22</v>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>85-77</t>
+        </is>
+      </c>
+      <c r="G4" s="39" t="inlineStr">
+        <is>
+          <t>Division winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>IL Returns Only</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="C5" s="46" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D5" s="41" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="E5" s="40" t="n">
+        <v>23</v>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>86-76</t>
+        </is>
+      </c>
+      <c r="G5" s="39" t="inlineStr">
+        <is>
+          <t>Division winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>IL Returns + Ward + Dominguez</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="C6" s="46" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D6" s="41" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="E6" s="40" t="n">
+        <v>23</v>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>86-76</t>
+        </is>
+      </c>
+      <c r="G6" s="39" t="inlineStr">
+        <is>
+          <t>Division winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="38" t="inlineStr">
+        <is>
+          <t>Worst Case - IL returns slip/setback</t>
+        </is>
+      </c>
+      <c r="B7" s="46" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="C7" s="46" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="D7" s="41" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="E7" s="40" t="n">
+        <v>23</v>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>86-76</t>
+        </is>
+      </c>
+      <c r="G7" s="39" t="inlineStr">
+        <is>
+          <t>Division winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>Optimistic IL - Everyone Returns Early</t>
+        </is>
+      </c>
+      <c r="B8" s="46" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="C8" s="46" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="D8" s="41" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="E8" s="40" t="n">
+        <v>23</v>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>86-76</t>
+        </is>
+      </c>
+      <c r="G8" s="39" t="inlineStr">
+        <is>
+          <t>Division winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>Pessimistic IL - Setbacks, Late Returns</t>
+        </is>
+      </c>
+      <c r="B9" s="46" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="C9" s="46" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="D9" s="41" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="E9" s="40" t="n">
+        <v>23</v>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>86-76</t>
+        </is>
+      </c>
+      <c r="G9" s="39" t="inlineStr">
+        <is>
+          <t>Division winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>BASELINE - NO IL RETURNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>RS/G</t>
+        </is>
+      </c>
+      <c r="B12" s="62" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>RA/G</t>
+        </is>
+      </c>
+      <c r="B13" s="62" t="n">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Win%</t>
+        </is>
+      </c>
+      <c r="B14" s="62" t="n">
+        <v>0.455</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Luck wins</t>
+        </is>
+      </c>
+      <c r="B15" s="62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>Final W-L</t>
+        </is>
+      </c>
+      <c r="B16" s="62" t="inlineStr">
+        <is>
+          <t>85-77</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>Playoff</t>
+        </is>
+      </c>
+      <c r="B17" s="62" t="inlineStr">
+        <is>
+          <t>Division winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>vs TEX</t>
+        </is>
+      </c>
+      <c r="B18" s="62" t="inlineStr">
+        <is>
+          <t>+2 games</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>vs HOU</t>
+        </is>
+      </c>
+      <c r="B19" s="62" t="inlineStr">
+        <is>
+          <t>+6 games</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>IL RETURNS ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>RS/G</t>
+        </is>
+      </c>
+      <c r="B22" s="62" t="n">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>RA/G</t>
+        </is>
+      </c>
+      <c r="B23" s="62" t="n">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Win%</t>
+        </is>
+      </c>
+      <c r="B24" s="62" t="n">
+        <v>0.486</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Luck wins</t>
+        </is>
+      </c>
+      <c r="B25" s="62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Final W-L</t>
+        </is>
+      </c>
+      <c r="B26" s="62" t="inlineStr">
+        <is>
+          <t>86-76</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Playoff</t>
+        </is>
+      </c>
+      <c r="B27" s="62" t="inlineStr">
+        <is>
+          <t>Division winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>vs TEX</t>
+        </is>
+      </c>
+      <c r="B28" s="62" t="inlineStr">
+        <is>
+          <t>+3 games</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>vs HOU</t>
+        </is>
+      </c>
+      <c r="B29" s="62" t="inlineStr">
+        <is>
+          <t>+7 games</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>RS/G impact</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>RA/G impact</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Will Wilson</t>
+        </is>
+      </c>
+      <c r="B31" s="40" t="inlineStr">
+        <is>
+          <t>+0.008</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>Bench depth -- confirmed still on 60-day IL (thumb) as of Aug 6-9, no target date reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>IL return: J.P. Crawford</t>
+        </is>
+      </c>
+      <c r="B32" s="40" t="inlineStr">
+        <is>
+          <t>+0.068</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>Elite OBP/walk rate -- still on IL as of Aug 14 (confirmed via live bbref fetch), well past the earlier Aug 2 estimate. Re-verify before trusting this date either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Cole Wilcox</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>-0.027</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>Left oblique strain, placed Aug 7. Was a dependable reliever pre-injury (4.00 ERA, 27 IP) -- no official target date reported yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Matt Brash</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C34" s="40" t="inlineStr">
+        <is>
+          <t>-0.100</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>0.54 ERA closer -- right lat inflammation, targeting Aug 22-28 return</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Carlos Vargas</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C35" s="40" t="inlineStr">
+        <is>
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>Bullpen depth -- right lat strain, beginning rehab assignment as of mid-Aug after missing 116 straight games</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Cooper Criswell</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" s="40" t="inlineStr">
+        <is>
+          <t>-0.034</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>Right shoulder/pec strain -- targeting Aug 28-Sept 1 return</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>IL RETURNS + WARD + DOMINGUEZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>RS/G</t>
+        </is>
+      </c>
+      <c r="B39" s="62" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>RA/G</t>
+        </is>
+      </c>
+      <c r="B40" s="62" t="n">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>Win%</t>
+        </is>
+      </c>
+      <c r="B41" s="62" t="n">
+        <v>0.488</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t>Luck wins</t>
+        </is>
+      </c>
+      <c r="B42" s="62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>Final W-L</t>
+        </is>
+      </c>
+      <c r="B43" s="62" t="inlineStr">
+        <is>
+          <t>86-76</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>Playoff</t>
+        </is>
+      </c>
+      <c r="B44" s="62" t="inlineStr">
+        <is>
+          <t>Division winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>vs TEX</t>
+        </is>
+      </c>
+      <c r="B45" s="62" t="inlineStr">
+        <is>
+          <t>+3 games</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t>vs HOU</t>
+        </is>
+      </c>
+      <c r="B46" s="62" t="inlineStr">
+        <is>
+          <t>+7 games</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>RS/G impact</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>RA/G impact</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Will Wilson</t>
+        </is>
+      </c>
+      <c r="B48" s="40" t="inlineStr">
+        <is>
+          <t>+0.008</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="22" t="inlineStr">
+        <is>
+          <t>Bench depth -- confirmed still on 60-day IL (thumb) as of Aug 6-9, no target date reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>IL return: J.P. Crawford</t>
+        </is>
+      </c>
+      <c r="B49" s="40" t="inlineStr">
+        <is>
+          <t>+0.068</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="inlineStr">
+        <is>
+          <t>Elite OBP/walk rate -- still on IL as of Aug 14 (confirmed via live bbref fetch), well past the earlier Aug 2 estimate. Re-verify before trusting this date either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Cole Wilcox</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C50" s="40" t="inlineStr">
+        <is>
+          <t>-0.027</t>
+        </is>
+      </c>
+      <c r="D50" s="22" t="inlineStr">
+        <is>
+          <t>Left oblique strain, placed Aug 7. Was a dependable reliever pre-injury (4.00 ERA, 27 IP) -- no official target date reported yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Matt Brash</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C51" s="40" t="inlineStr">
+        <is>
+          <t>-0.100</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr">
+        <is>
+          <t>0.54 ERA closer -- right lat inflammation, targeting Aug 22-28 return</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Carlos Vargas</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C52" s="40" t="inlineStr">
+        <is>
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>Bullpen depth -- right lat strain, beginning rehab assignment as of mid-Aug after missing 116 straight games</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Cooper Criswell</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C53" s="40" t="inlineStr">
+        <is>
+          <t>-0.034</t>
+        </is>
+      </c>
+      <c r="D53" s="22" t="inlineStr">
+        <is>
+          <t>Right shoulder/pec strain -- targeting Aug 28-Sept 1 return</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="21" t="inlineStr">
+        <is>
+          <t>Acquired: Taylor Ward</t>
+        </is>
+      </c>
+      <c r="B54" s="40" t="inlineStr">
+        <is>
+          <t>+0.020</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="22" t="inlineStr">
+        <is>
+          <t>Acquired from BAL 2026-08-03. Rough Mariners debut so far (8 G, .375 OPS) -- small sample, already reflected in team-wide stats, watch for regression toward his established .729 OPS rate either way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="21" t="inlineStr">
+        <is>
+          <t>Acquired: Seranthony Dominguez</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="inlineStr">
+        <is>
+          <t>Acquired from CHW 2026-08-03 for Castillo. Rough Mariners debut (5 G, 3.1 IP, 10.80 ERA) -- tiny sample, already reflected in team-wide stats. Was already a modest-at-best add per deadline_trade_comparison.py's stat-by-stat breakdown even before this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>WORST CASE - IL RETURNS SLIP/SETBACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="21" t="inlineStr">
+        <is>
+          <t>RS/G</t>
+        </is>
+      </c>
+      <c r="B58" s="62" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="21" t="inlineStr">
+        <is>
+          <t>RA/G</t>
+        </is>
+      </c>
+      <c r="B59" s="62" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="inlineStr">
+        <is>
+          <t>Win%</t>
+        </is>
+      </c>
+      <c r="B60" s="62" t="n">
+        <v>0.477</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="21" t="inlineStr">
+        <is>
+          <t>Luck wins</t>
+        </is>
+      </c>
+      <c r="B61" s="62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="21" t="inlineStr">
+        <is>
+          <t>Final W-L</t>
+        </is>
+      </c>
+      <c r="B62" s="62" t="inlineStr">
+        <is>
+          <t>86-76</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="21" t="inlineStr">
+        <is>
+          <t>Playoff</t>
+        </is>
+      </c>
+      <c r="B63" s="62" t="inlineStr">
+        <is>
+          <t>Division winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="21" t="inlineStr">
+        <is>
+          <t>vs TEX</t>
+        </is>
+      </c>
+      <c r="B64" s="62" t="inlineStr">
+        <is>
+          <t>+3 games</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="21" t="inlineStr">
+        <is>
+          <t>vs HOU</t>
+        </is>
+      </c>
+      <c r="B65" s="62" t="inlineStr">
+        <is>
+          <t>+7 games</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>RS/G impact</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>RA/G impact</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="21" t="inlineStr">
+        <is>
+          <t>IL return: J.P. Crawford</t>
+        </is>
+      </c>
+      <c r="B67" s="40" t="inlineStr">
+        <is>
+          <t>+0.038</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D67" s="22" t="inlineStr">
+        <is>
+          <t>Elite OBP/walk rate -- still on IL as of Aug 14 (confirmed via live bbref fetch), well past the earlier Aug 2 estimate. Re-verify before trusting this date either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Cole Wilcox</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C68" s="40" t="inlineStr">
+        <is>
+          <t>-0.016</t>
+        </is>
+      </c>
+      <c r="D68" s="22" t="inlineStr">
+        <is>
+          <t>Left oblique strain, placed Aug 7. Was a dependable reliever pre-injury (4.00 ERA, 27 IP) -- no official target date reported yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Matt Brash</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C69" s="40" t="inlineStr">
+        <is>
+          <t>-0.079</t>
+        </is>
+      </c>
+      <c r="D69" s="22" t="inlineStr">
+        <is>
+          <t>0.54 ERA closer -- right lat inflammation, targeting Aug 22-28 return</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Carlos Vargas</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="40" t="inlineStr">
+        <is>
+          <t>-0.046</t>
+        </is>
+      </c>
+      <c r="D70" s="22" t="inlineStr">
+        <is>
+          <t>Bullpen depth -- right lat strain, beginning rehab assignment as of mid-Aug after missing 116 straight games</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Cooper Criswell</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C71" s="40" t="inlineStr">
+        <is>
+          <t>-0.027</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="inlineStr">
+        <is>
+          <t>Right shoulder/pec strain -- targeting Aug 28-Sept 1 return</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>OPTIMISTIC IL - EVERYONE RETURNS EARLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="21" t="inlineStr">
+        <is>
+          <t>RS/G</t>
+        </is>
+      </c>
+      <c r="B74" s="62" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="21" t="inlineStr">
+        <is>
+          <t>RA/G</t>
+        </is>
+      </c>
+      <c r="B75" s="62" t="n">
+        <v>4.14</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="21" t="inlineStr">
+        <is>
+          <t>Win%</t>
+        </is>
+      </c>
+      <c r="B76" s="62" t="n">
+        <v>0.494</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="21" t="inlineStr">
+        <is>
+          <t>Luck wins</t>
+        </is>
+      </c>
+      <c r="B77" s="62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="21" t="inlineStr">
+        <is>
+          <t>Final W-L</t>
+        </is>
+      </c>
+      <c r="B78" s="62" t="inlineStr">
+        <is>
+          <t>86-76</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="21" t="inlineStr">
+        <is>
+          <t>Playoff</t>
+        </is>
+      </c>
+      <c r="B79" s="62" t="inlineStr">
+        <is>
+          <t>Division winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="21" t="inlineStr">
+        <is>
+          <t>vs TEX</t>
+        </is>
+      </c>
+      <c r="B80" s="62" t="inlineStr">
+        <is>
+          <t>+3 games</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="21" t="inlineStr">
+        <is>
+          <t>vs HOU</t>
+        </is>
+      </c>
+      <c r="B81" s="62" t="inlineStr">
+        <is>
+          <t>+7 games</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>RS/G impact</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>RA/G impact</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Will Wilson</t>
+        </is>
+      </c>
+      <c r="B83" s="40" t="inlineStr">
+        <is>
+          <t>+0.016</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D83" s="22" t="inlineStr">
+        <is>
+          <t>Bench depth -- confirmed still on 60-day IL (thumb) as of Aug 6-9, no target date reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="21" t="inlineStr">
+        <is>
+          <t>IL return: J.P. Crawford</t>
+        </is>
+      </c>
+      <c r="B84" s="40" t="inlineStr">
+        <is>
+          <t>+0.100</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D84" s="22" t="inlineStr">
+        <is>
+          <t>Elite OBP/walk rate -- still on IL as of Aug 14 (confirmed via live bbref fetch), well past the earlier Aug 2 estimate. Re-verify before trusting this date either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Cole Wilcox</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C85" s="40" t="inlineStr">
+        <is>
+          <t>-0.030</t>
+        </is>
+      </c>
+      <c r="D85" s="22" t="inlineStr">
+        <is>
+          <t>Left oblique strain, placed Aug 7. Was a dependable reliever pre-injury (4.00 ERA, 27 IP) -- no official target date reported yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Matt Brash</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C86" s="40" t="inlineStr">
+        <is>
+          <t>-0.100</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="inlineStr">
+        <is>
+          <t>0.54 ERA closer -- right lat inflammation, targeting Aug 22-28 return</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Carlos Vargas</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C87" s="40" t="inlineStr">
+        <is>
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="D87" s="22" t="inlineStr">
+        <is>
+          <t>Bullpen depth -- right lat strain, beginning rehab assignment as of mid-Aug after missing 116 straight games</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Cooper Criswell</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C88" s="40" t="inlineStr">
+        <is>
+          <t>-0.036</t>
+        </is>
+      </c>
+      <c r="D88" s="22" t="inlineStr">
+        <is>
+          <t>Right shoulder/pec strain -- targeting Aug 28-Sept 1 return</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="21" t="inlineStr">
+        <is>
+          <t>Acquired: Taylor Ward</t>
+        </is>
+      </c>
+      <c r="B89" s="40" t="inlineStr">
+        <is>
+          <t>+0.020</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D89" s="22" t="inlineStr">
+        <is>
+          <t>Acquired from BAL 2026-08-03. Rough Mariners debut so far (8 G, .375 OPS) -- small sample, already reflected in team-wide stats, watch for regression toward his established .729 OPS rate either way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="21" t="inlineStr">
+        <is>
+          <t>Acquired: Seranthony Dominguez</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="inlineStr">
+        <is>
+          <t>Acquired from CHW 2026-08-03 for Castillo. Rough Mariners debut (5 G, 3.1 IP, 10.80 ERA) -- tiny sample, already reflected in team-wide stats. Was already a modest-at-best add per deadline_trade_comparison.py's stat-by-stat breakdown even before this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>PESSIMISTIC IL - SETBACKS, LATE RETURNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="21" t="inlineStr">
+        <is>
+          <t>RS/G</t>
+        </is>
+      </c>
+      <c r="B93" s="62" t="n">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="21" t="inlineStr">
+        <is>
+          <t>RA/G</t>
+        </is>
+      </c>
+      <c r="B94" s="62" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="21" t="inlineStr">
+        <is>
+          <t>Win%</t>
+        </is>
+      </c>
+      <c r="B95" s="62" t="n">
+        <v>0.479</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="21" t="inlineStr">
+        <is>
+          <t>Luck wins</t>
+        </is>
+      </c>
+      <c r="B96" s="62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="21" t="inlineStr">
+        <is>
+          <t>Final W-L</t>
+        </is>
+      </c>
+      <c r="B97" s="62" t="inlineStr">
+        <is>
+          <t>86-76</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="21" t="inlineStr">
+        <is>
+          <t>Playoff</t>
+        </is>
+      </c>
+      <c r="B98" s="62" t="inlineStr">
+        <is>
+          <t>Division winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="21" t="inlineStr">
+        <is>
+          <t>vs TEX</t>
+        </is>
+      </c>
+      <c r="B99" s="62" t="inlineStr">
+        <is>
+          <t>+3 games</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="21" t="inlineStr">
+        <is>
+          <t>vs HOU</t>
+        </is>
+      </c>
+      <c r="B100" s="62" t="inlineStr">
+        <is>
+          <t>+7 games</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>RS/G impact</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>RA/G impact</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="21" t="inlineStr">
+        <is>
+          <t>IL return: J.P. Crawford</t>
+        </is>
+      </c>
+      <c r="B102" s="40" t="inlineStr">
+        <is>
+          <t>+0.038</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="inlineStr">
+        <is>
+          <t>Elite OBP/walk rate -- still on IL as of Aug 14 (confirmed via live bbref fetch), well past the earlier Aug 2 estimate. Re-verify before trusting this date either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Cole Wilcox</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C103" s="40" t="inlineStr">
+        <is>
+          <t>-0.016</t>
+        </is>
+      </c>
+      <c r="D103" s="22" t="inlineStr">
+        <is>
+          <t>Left oblique strain, placed Aug 7. Was a dependable reliever pre-injury (4.00 ERA, 27 IP) -- no official target date reported yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Matt Brash</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C104" s="40" t="inlineStr">
+        <is>
+          <t>-0.079</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="inlineStr">
+        <is>
+          <t>0.54 ERA closer -- right lat inflammation, targeting Aug 22-28 return</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Carlos Vargas</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C105" s="40" t="inlineStr">
+        <is>
+          <t>-0.046</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="inlineStr">
+        <is>
+          <t>Bullpen depth -- right lat strain, beginning rehab assignment as of mid-Aug after missing 116 straight games</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="21" t="inlineStr">
+        <is>
+          <t>IL return: Cooper Criswell</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C106" s="40" t="inlineStr">
+        <is>
+          <t>-0.027</t>
+        </is>
+      </c>
+      <c r="D106" s="22" t="inlineStr">
+        <is>
+          <t>Right shoulder/pec strain -- targeting Aug 28-Sept 1 return</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="21" t="inlineStr">
+        <is>
+          <t>Acquired: Taylor Ward</t>
+        </is>
+      </c>
+      <c r="B107" s="40" t="inlineStr">
+        <is>
+          <t>+0.020</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D107" s="22" t="inlineStr">
+        <is>
+          <t>Acquired from BAL 2026-08-03. Rough Mariners debut so far (8 G, .375 OPS) -- small sample, already reflected in team-wide stats, watch for regression toward his established .729 OPS rate either way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="21" t="inlineStr">
+        <is>
+          <t>Acquired: Seranthony Dominguez</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D108" s="22" t="inlineStr">
+        <is>
+          <t>Acquired from CHW 2026-08-03 for Castillo. Rough Mariners debut (5 G, 3.1 IP, 10.80 ERA) -- tiny sample, already reflected in team-wide stats. Was already a modest-at-best add per deadline_trade_comparison.py's stat-by-stat breakdown even before this.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="56">
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="B98:G98"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B78:G78"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B99:G99"/>
+    <mergeCell ref="A92:G92"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B80:G80"/>
+    <mergeCell ref="B95:G95"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B94:G94"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B79:G79"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B97:G97"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B100:G100"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B81:G81"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B59:G59"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B93:G93"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="B96:G96"/>
+    <mergeCell ref="B39:G39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>